--- a/ESD Project.xlsx
+++ b/ESD Project.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
   <si>
     <t>Sr. No</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t>completed</t>
+  </si>
+  <si>
+    <t>can interface</t>
   </si>
   <si>
     <t>Bootloaders for Stm32</t>
@@ -104,7 +107,7 @@
 4.prepare git repo</t>
   </si>
   <si>
-    <t>Project Title:- Secure OTA Firmware Management System for RTOS-Based ECU Networks</t>
+    <t>Project Title:- Secure OTA Firmware Management System for RTOS-Based ECU Networks                                     flow :- CAN Network → BeagleBone Linux → MQTT Dashboard →FreeRTOS → UART Communication → Flash Programming → Bootloader → OTA Protocol → Security → System Testing</t>
   </si>
 </sst>
 </file>
@@ -163,7 +166,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -391,20 +394,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -416,6 +419,12 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -836,373 +845,373 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="44" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="45" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="45" width="22.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="44" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="45" width="33.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="46" width="29.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="46" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="47" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="47" width="22.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="46" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="47" width="33.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="48" width="29.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
-      <c r="A1" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="C1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="F1" s="16" t="s">
         <v>16</v>
       </c>
+      <c r="G1" s="16" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
-      <c r="A2" s="15">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="18">
         <v>46203</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="19">
+      <c r="D2" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="21">
         <v>46173</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>20</v>
       </c>
+      <c r="G2" s="23" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="26"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="28"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="26"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="28"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
-      <c r="A5" s="22"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="26"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="28"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="31"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="33"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="5"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>2</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="18">
         <v>46175</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="21">
+        <v>46176</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="36"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="37"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="122.25">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="19">
-        <v>46176</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="34"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="35"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="35"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="35"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="22.5">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="36"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="5"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>3</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="35"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="25"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="37"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="35"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="37"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="23"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="35"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="37"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="22.5">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="36"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="5"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="33"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
       <c r="G19" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
-      <c r="A20" s="41">
+      <c r="A20" s="43">
         <v>4</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
       <c r="A21" s="5"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21.75">
       <c r="A22" s="5"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="33"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
       <c r="A23" s="5"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
       <c r="A24" s="5"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="33"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="5"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="33"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="5"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="5"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="34"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="5"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="5"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
       <c r="G29" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="5"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="34"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="6"/>
     </row>
   </sheetData>
@@ -1235,204 +1244,237 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="50.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="13" width="50.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="9" t="s">
-        <v>7</v>
-      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="7" t="s">
-        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="5"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="5"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="5"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="5"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="5"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="5"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="5"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="5"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="5"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="5"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="5"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="5"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="5"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ESD Project.xlsx
+++ b/ESD Project.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>Sr. No</t>
   </si>
@@ -107,7 +107,10 @@
 4.prepare git repo</t>
   </si>
   <si>
-    <t>Project Title:- Secure OTA Firmware Management System for RTOS-Based ECU Networks                                     flow :- CAN Network → BeagleBone Linux → MQTT Dashboard →FreeRTOS → UART Communication → Flash Programming → Bootloader → OTA Protocol → Security → System Testing</t>
+    <t xml:space="preserve">Project Title:- Secure OTA Firmware Management System for RTOS-Based ECU Networks                                     </t>
+  </si>
+  <si>
+    <t>1. flow :- CAN Network → BeagleBone Linux → IoT Dashboard →FreeRTOS → UART Communication → Flash Programming → Bootloader → OTA Protocol → Security → System Testing</t>
   </si>
 </sst>
 </file>
@@ -850,7 +853,7 @@
     <col min="3" max="3" style="47" width="58.71928571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="47" width="22.14785714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="46" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="47" width="33.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="47" width="57.71928571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="48" width="29.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -1031,13 +1034,17 @@
       <c r="A14" s="17">
         <v>3</v>
       </c>
-      <c r="B14" s="18"/>
+      <c r="B14" s="18">
+        <v>46178</v>
+      </c>
       <c r="C14" s="39"/>
       <c r="D14" s="20" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="21"/>
-      <c r="F14" s="40"/>
+      <c r="F14" s="40" t="s">
+        <v>28</v>
+      </c>
       <c r="G14" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">

--- a/ESD Project.xlsx
+++ b/ESD Project.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t>Sr. No</t>
   </si>
@@ -110,7 +110,13 @@
     <t xml:space="preserve">Project Title:- Secure OTA Firmware Management System for RTOS-Based ECU Networks                                     </t>
   </si>
   <si>
-    <t>1. flow :- CAN Network → BeagleBone Linux → IoT Dashboard →FreeRTOS → UART Communication → Flash Programming → Bootloader → OTA Protocol → Security → System Testing</t>
+    <t xml:space="preserve">3.AWS when IOT starts  </t>
+  </si>
+  <si>
+    <t>1.CAN COMMUNICATION between 2 stms(IMPORTANT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. flow :- CAN Network → BeagleBone Linux →                          IoT Dashboard →FreeRTOS  → UART Communication → Flash Programming → Bootloader → OTA Protocol → Security → System Testing                                                                 </t>
   </si>
 </sst>
 </file>
@@ -120,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +152,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -397,20 +409,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -423,79 +438,82 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -504,34 +522,34 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="8" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="8" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="9" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -848,378 +866,384 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="46" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="47" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="47" width="22.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="46" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="47" width="57.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="48" width="29.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="48" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="49" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="49" width="22.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="48" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="49" width="57.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="50" width="29.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
-      <c r="A2" s="17">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="20">
         <v>46203</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="23">
         <v>46173</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="25" t="s">
         <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="28"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="30"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="28"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="30"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="28"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="30"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="23.25">
+      <c r="A6" s="31"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
-      <c r="A8" s="17">
+      <c r="A7" s="6"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="20">
         <v>46175</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="23">
         <v>46176</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="36"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="27" t="s">
+      <c r="G8" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="27" t="s">
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="39"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27" t="s">
+      <c r="E10" s="27"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="39"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="22.5">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="122.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="39"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="23.25">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="38"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="40"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="5"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
-      <c r="A14" s="17">
+      <c r="A13" s="6"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="22.5">
+      <c r="A14" s="19">
         <v>3</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="20">
         <v>46178</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="36"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="27" t="s">
+      <c r="E14" s="23">
+        <v>46181</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="38"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="22.5">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="27" t="s">
+      <c r="E15" s="27"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="39"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="22.5">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="27" t="s">
+      <c r="E16" s="27"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="39"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="22.5">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="32" t="s">
+      <c r="E17" s="27"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="39"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33.75">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="38"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="40"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="5"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
-      <c r="A20" s="43">
+      <c r="A19" s="6"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="22.5">
+      <c r="A20" s="45">
         <v>4</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="44" t="s">
+      <c r="B20" s="36"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
-      <c r="A21" s="5"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="45" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="22.5">
+      <c r="A21" s="6"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21.75">
-      <c r="A22" s="5"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="44" t="s">
+      <c r="E21" s="36"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="22.5">
+      <c r="A22" s="6"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="6"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
-      <c r="A23" s="5"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="45" t="s">
+      <c r="A23" s="6"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="6"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
-      <c r="A24" s="5"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="44" t="s">
+      <c r="A24" s="6"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="6"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="5"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="6"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="5"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="44" t="s">
+      <c r="A26" s="6"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="6"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="5"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="45" t="s">
+      <c r="A27" s="6"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="6"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="5"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="44" t="s">
+      <c r="A28" s="6"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="6"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="5"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="45" t="s">
+      <c r="A29" s="6"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="6"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="5"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="44" t="s">
+      <c r="A30" s="6"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="6"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1254,13 +1278,13 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="50.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="50.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1274,214 +1298,214 @@
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="8" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="11" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="7" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="5"/>
+      <c r="A8" s="6"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="5"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="5"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="5"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="5"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="5"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="5"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="5"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="5"/>
+      <c r="A17" s="6"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="5"/>
+      <c r="A18" s="6"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="5"/>
+      <c r="A19" s="6"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="5"/>
+      <c r="A20" s="6"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ESD Project.xlsx
+++ b/ESD Project.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
   <si>
     <t>Sr. No</t>
   </si>
@@ -26,28 +26,61 @@
     <t>Status</t>
   </si>
   <si>
+    <t>flow</t>
+  </si>
+  <si>
     <t>Hardware and Software interface Stm32 and Beagle Bone CAN network</t>
   </si>
   <si>
     <t>not started</t>
   </si>
   <si>
+    <t xml:space="preserve"> CAN Network →                                                               </t>
+  </si>
+  <si>
     <t>completed</t>
   </si>
   <si>
     <t>can interface</t>
   </si>
   <si>
+    <t xml:space="preserve">BeagleBone Linux → </t>
+  </si>
+  <si>
     <t>Bootloaders for Stm32</t>
   </si>
   <si>
+    <t xml:space="preserve">   IoT Dashboard →</t>
+  </si>
+  <si>
     <t>in progress</t>
   </si>
   <si>
     <t xml:space="preserve">BeagleBone Black Linux Gateway OTA Server Agent  </t>
   </si>
   <si>
+    <t xml:space="preserve">  FreeRTOS  → </t>
+  </si>
+  <si>
     <t>IoT Dashboard   aws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        UART Communication →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Flash Programming →</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bootloader → </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTA Protocol→  </t>
+  </si>
+  <si>
+    <t>Security →</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> System Testing   </t>
   </si>
   <si>
     <t>Sr .No</t>
@@ -116,7 +149,7 @@
     <t>1.CAN COMMUNICATION between 2 stms(IMPORTANT)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. flow :- CAN Network → BeagleBone Linux →                          IoT Dashboard →FreeRTOS  → UART Communication → Flash Programming → Bootloader → OTA Protocol → Security → System Testing                                                                 </t>
+    <t/>
   </si>
 </sst>
 </file>
@@ -142,6 +175,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -156,7 +195,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -177,12 +216,6 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -414,136 +447,136 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
@@ -875,30 +908,30 @@
     <col min="7" max="7" style="50" width="29.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="16" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+        <v>28</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="22.5">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -906,49 +939,49 @@
         <v>46203</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E2" s="23">
         <v>46173</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
       <c r="A3" s="26"/>
       <c r="B3" s="27"/>
       <c r="C3" s="28"/>
       <c r="D3" s="29" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="28"/>
       <c r="G3" s="30"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22.5">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="28"/>
       <c r="D4" s="29" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="28"/>
       <c r="G4" s="30"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5">
       <c r="A5" s="26"/>
       <c r="B5" s="27"/>
       <c r="C5" s="28"/>
       <c r="D5" s="29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="28"/>
@@ -959,7 +992,7 @@
       <c r="B6" s="32"/>
       <c r="C6" s="33"/>
       <c r="D6" s="34" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="33"/>
@@ -982,19 +1015,19 @@
         <v>46175</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E8" s="23">
         <v>46176</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5">
@@ -1002,7 +1035,7 @@
       <c r="B9" s="27"/>
       <c r="C9" s="28"/>
       <c r="D9" s="29" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E9" s="27"/>
       <c r="F9" s="28"/>
@@ -1013,7 +1046,7 @@
       <c r="B10" s="27"/>
       <c r="C10" s="28"/>
       <c r="D10" s="29" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="28"/>
@@ -1024,7 +1057,7 @@
       <c r="B11" s="27"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="28"/>
@@ -1035,7 +1068,7 @@
       <c r="B12" s="32"/>
       <c r="C12" s="33"/>
       <c r="D12" s="34" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="33"/>
@@ -1058,16 +1091,16 @@
         <v>46178</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E14" s="23">
         <v>46181</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G14" s="38"/>
     </row>
@@ -1076,7 +1109,7 @@
       <c r="B15" s="27"/>
       <c r="C15" s="43"/>
       <c r="D15" s="29" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="43"/>
@@ -1087,7 +1120,7 @@
       <c r="B16" s="27"/>
       <c r="C16" s="43"/>
       <c r="D16" s="29" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="43"/>
@@ -1098,18 +1131,18 @@
       <c r="B17" s="27"/>
       <c r="C17" s="43"/>
       <c r="D17" s="29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="43"/>
       <c r="G17" s="39"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="23.25">
       <c r="A18" s="31"/>
       <c r="B18" s="32"/>
       <c r="C18" s="44"/>
       <c r="D18" s="34" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="44"/>
@@ -1131,7 +1164,7 @@
       <c r="B20" s="36"/>
       <c r="C20" s="37"/>
       <c r="D20" s="46" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -1142,7 +1175,7 @@
       <c r="B21" s="36"/>
       <c r="C21" s="37"/>
       <c r="D21" s="47" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E21" s="36"/>
       <c r="F21" s="37"/>
@@ -1153,7 +1186,7 @@
       <c r="B22" s="36"/>
       <c r="C22" s="37"/>
       <c r="D22" s="46" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E22" s="36"/>
       <c r="F22" s="37"/>
@@ -1164,7 +1197,7 @@
       <c r="B23" s="36"/>
       <c r="C23" s="37"/>
       <c r="D23" s="47" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E23" s="36"/>
       <c r="F23" s="37"/>
@@ -1175,7 +1208,7 @@
       <c r="B24" s="36"/>
       <c r="C24" s="37"/>
       <c r="D24" s="46" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E24" s="36"/>
       <c r="F24" s="37"/>
@@ -1195,7 +1228,7 @@
       <c r="B26" s="36"/>
       <c r="C26" s="37"/>
       <c r="D26" s="46" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E26" s="36"/>
       <c r="F26" s="37"/>
@@ -1206,7 +1239,7 @@
       <c r="B27" s="36"/>
       <c r="C27" s="37"/>
       <c r="D27" s="47" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E27" s="36"/>
       <c r="F27" s="37"/>
@@ -1217,7 +1250,7 @@
       <c r="B28" s="36"/>
       <c r="C28" s="37"/>
       <c r="D28" s="46" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E28" s="36"/>
       <c r="F28" s="37"/>
@@ -1228,7 +1261,7 @@
       <c r="B29" s="36"/>
       <c r="C29" s="37"/>
       <c r="D29" s="47" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E29" s="36"/>
       <c r="F29" s="37"/>
@@ -1239,7 +1272,7 @@
       <c r="B30" s="36"/>
       <c r="C30" s="37"/>
       <c r="D30" s="46" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
@@ -1282,8 +1315,8 @@
     <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="15" width="50.29071428571429" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="5.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="23.433571428571426" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -1299,7 +1332,9 @@
         <v>2</v>
       </c>
       <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="G1" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
@@ -1308,15 +1343,17 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="G2" s="9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -1325,11 +1362,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G3" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -1338,15 +1377,17 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="G4" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -1355,15 +1396,17 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G5" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -1372,13 +1415,15 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G6" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -1387,7 +1432,9 @@
       <c r="C7" s="5"/>
       <c r="D7" s="8"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G7" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -1396,7 +1443,9 @@
       <c r="C8" s="5"/>
       <c r="D8" s="8"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="G8" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -1405,7 +1454,9 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G9" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -1414,7 +1465,9 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G10" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -1423,7 +1476,9 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="G11" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">

--- a/ESD Project.xlsx
+++ b/ESD Project.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve"> CAN Network →                                                               </t>
   </si>
   <si>
+    <t>can interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BeagleBone Linux → </t>
+  </si>
+  <si>
     <t>completed</t>
-  </si>
-  <si>
-    <t>can interface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BeagleBone Linux → </t>
   </si>
   <si>
     <t>Bootloaders for Stm32</t>
@@ -149,7 +149,7 @@
     <t>1.CAN COMMUNICATION between 2 stms(IMPORTANT)</t>
   </si>
   <si>
-    <t/>
+    <t>key tasks of can communication in the project1. Heartbeat Monitoring2. ECU Discovery3. Device Status Reporting4. Command Distribution5. Firmware Version Reporting6. OTA Update Trigger7. Firmware Transfer 8. ACK/NACK Mechanism9. OTA Progress Reporting10. Error Diagnostics</t>
   </si>
 </sst>
 </file>
@@ -159,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,7 +176,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -191,12 +191,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -442,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -471,11 +465,8 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -484,105 +475,105 @@
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="9" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="8" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="8" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -899,383 +890,383 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="48" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="49" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="49" width="22.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="48" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="49" width="57.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="50" width="29.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="47" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="48" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="48" width="22.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="47" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="48" width="57.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="49" width="29.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="22.5">
-      <c r="A2" s="19">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>46203</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="22">
         <v>46173</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="24" t="s">
         <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="30"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="29"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22.5">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="30"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="29"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="30"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="29"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="23.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34" t="s">
+      <c r="A6" s="30"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="35"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="34"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
       <c r="G7" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>46175</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <v>46176</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="37" t="s">
         <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="39"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="39"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="22.5">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="39"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="23.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="40"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="6"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="36"/>
       <c r="G13" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="22.5">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>3</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="19">
         <v>46178</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="22">
         <v>46181</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="38"/>
+      <c r="G14" s="37"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="22.5">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="29" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="39"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="22.5">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="29" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="39"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="29" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="39"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="23.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="34" t="s">
+      <c r="A18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="40"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="6"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
       <c r="G19" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="22.5">
-      <c r="A20" s="45">
+      <c r="A20" s="44">
         <v>4</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="46" t="s">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="37"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36"/>
       <c r="G20" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="22.5">
       <c r="A21" s="6"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="47" t="s">
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="36"/>
       <c r="G21" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="22.5">
       <c r="A22" s="6"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="46" t="s">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36"/>
       <c r="G22" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
       <c r="A23" s="6"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="47" t="s">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36"/>
       <c r="G23" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
       <c r="A24" s="6"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="46" t="s">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="37"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="36"/>
       <c r="G24" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="6"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="37"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="36"/>
       <c r="G25" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="6"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="46" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="37"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="47" t="s">
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="37"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="36"/>
       <c r="G27" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="6"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="46" t="s">
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="37"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="36"/>
       <c r="G28" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="6"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="47" t="s">
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="36"/>
-      <c r="F29" s="37"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="36"/>
       <c r="G29" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="6"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="46" t="s">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="37"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="36"/>
       <c r="G30" s="7"/>
     </row>
   </sheetData>
@@ -1311,16 +1302,16 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="15" width="50.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="5.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="15" width="23.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="50.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="5.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="23.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1337,7 +1328,7 @@
       </c>
       <c r="G1" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1352,26 +1343,26 @@
       <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -1386,11 +1377,11 @@
       <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -1409,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -1426,7 +1417,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
@@ -1437,7 +1428,7 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
@@ -1448,7 +1439,7 @@
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
@@ -1459,7 +1450,7 @@
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="5"/>
@@ -1470,7 +1461,7 @@
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6"/>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
@@ -1481,7 +1472,7 @@
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6"/>
       <c r="B12" s="2"/>
       <c r="C12" s="5"/>
@@ -1490,7 +1481,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6"/>
       <c r="B13" s="2"/>
       <c r="C13" s="5"/>
@@ -1499,7 +1490,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6"/>
       <c r="B14" s="2"/>
       <c r="C14" s="5"/>

--- a/ESD Project.xlsx
+++ b/ESD Project.xlsx
@@ -1299,7 +1299,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="12" width="10.290714285714287" customWidth="1" bestFit="1"/>
@@ -1362,69 +1362,58 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6">
+        <v>4</v>
+      </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="8"/>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>5</v>
+      </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="5"/>
     </row>
@@ -1435,7 +1424,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" s="5"/>
     </row>
@@ -1443,10 +1432,10 @@
       <c r="A9" s="6"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="5"/>
     </row>
@@ -1457,7 +1446,7 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="5"/>
     </row>
@@ -1468,7 +1457,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="5"/>
     </row>
@@ -1478,7 +1467,9 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="G12" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -1499,7 +1490,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6"/>
       <c r="B15" s="2"/>
       <c r="C15" s="5"/>
@@ -1553,6 +1544,15 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="6"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
